--- a/data/trans_dic/P43B-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P43B-Edad-trans_dic.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,63%</t>
         </is>
       </c>
     </row>
@@ -635,32 +635,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,64; 40,02</t>
+          <t>4,39; 39,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,6; 57,92</t>
+          <t>10,7; 53,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,57; 68,55</t>
+          <t>11,4; 70,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,64; 40,02</t>
+          <t>4,39; 39,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,6; 57,92</t>
+          <t>10,7; 53,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,57; 68,55</t>
+          <t>11,4; 70,69</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -715,32 +715,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,85; 43,92</t>
+          <t>21,62; 43,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,01; 38,95</t>
+          <t>18,49; 38,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,84; 46,12</t>
+          <t>18,11; 43,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,85; 43,92</t>
+          <t>21,62; 43,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,01; 38,95</t>
+          <t>18,49; 38,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,84; 46,12</t>
+          <t>18,11; 43,48</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>34,93%</t>
         </is>
       </c>
     </row>
@@ -795,32 +795,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,84; 36,88</t>
+          <t>24,38; 36,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,78; 31,87</t>
+          <t>20,48; 31,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,83; 40,35</t>
+          <t>28,21; 41,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,84; 36,88</t>
+          <t>24,38; 36,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,78; 31,87</t>
+          <t>20,48; 31,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,83; 40,35</t>
+          <t>28,21; 41,79</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -875,32 +875,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,22; 22,72</t>
+          <t>14,1; 22,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,61; 19,91</t>
+          <t>12,61; 19,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,47; 31,5</t>
+          <t>25,73; 33,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,22; 22,72</t>
+          <t>14,1; 22,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,61; 19,91</t>
+          <t>12,61; 19,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,47; 31,5</t>
+          <t>25,73; 33,85</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,5; 11,57</t>
+          <t>5,65; 11,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 11,14</t>
+          <t>5,22; 11,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,24; 16,02</t>
+          <t>10,49; 16,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,5; 11,57</t>
+          <t>5,65; 11,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 11,14</t>
+          <t>5,22; 11,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,24; 16,02</t>
+          <t>10,49; 16,34</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -1035,32 +1035,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,98; 9,81</t>
+          <t>3,99; 10,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,35; 10,21</t>
+          <t>4,13; 10,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,77; 11,71</t>
+          <t>8,57; 14,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,98; 9,81</t>
+          <t>3,99; 10,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,35; 10,21</t>
+          <t>4,13; 10,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,77; 11,71</t>
+          <t>8,57; 14,26</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -1115,32 +1115,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 9,53</t>
+          <t>2,92; 9,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 7,65</t>
+          <t>1,13; 7,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,79; 10,92</t>
+          <t>5,87; 10,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 9,53</t>
+          <t>2,92; 9,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 7,65</t>
+          <t>1,13; 7,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,79; 10,92</t>
+          <t>5,87; 10,59</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -1195,32 +1195,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,4; 16,25</t>
+          <t>12,4; 16,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,7; 14,11</t>
+          <t>10,88; 14,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,23; 18,56</t>
+          <t>16,88; 20,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,4; 16,25</t>
+          <t>12,4; 16,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,7; 14,11</t>
+          <t>10,88; 14,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,23; 18,56</t>
+          <t>16,88; 20,34</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>8694</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>8694</t>
         </is>
       </c>
     </row>
@@ -1423,32 +1423,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1817; 10961</t>
+          <t>1202; 10888</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2171; 10834</t>
+          <t>2001; 9932</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2678; 14599</t>
+          <t>2501; 15508</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1817; 10961</t>
+          <t>1202; 10888</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2171; 10834</t>
+          <t>2001; 9932</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2678; 14599</t>
+          <t>2501; 15508</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16173</t>
+          <t>15751</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16173</t>
+          <t>15751</t>
         </is>
       </c>
     </row>
@@ -1541,32 +1541,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16999; 34173</t>
+          <t>16822; 33541</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12687; 27436</t>
+          <t>13020; 27036</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9780; 23940</t>
+          <t>9701; 23294</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16999; 34173</t>
+          <t>16822; 33541</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12687; 27436</t>
+          <t>13020; 27036</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9780; 23940</t>
+          <t>9701; 23294</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42190</t>
+          <t>49456</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42190</t>
+          <t>49456</t>
         </is>
       </c>
     </row>
@@ -1659,32 +1659,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>54887; 84897</t>
+          <t>56124; 83838</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43055; 69382</t>
+          <t>44589; 69451</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33863; 50926</t>
+          <t>39939; 59178</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>54887; 84897</t>
+          <t>56124; 83838</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>43055; 69382</t>
+          <t>44589; 69451</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33863; 50926</t>
+          <t>39939; 59178</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87286</t>
+          <t>94418</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87286</t>
+          <t>94418</t>
         </is>
       </c>
     </row>
@@ -1777,32 +1777,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>57060; 91148</t>
+          <t>56562; 91596</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52957; 83629</t>
+          <t>52958; 83949</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60299; 102880</t>
+          <t>81320; 106997</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>57060; 91148</t>
+          <t>56562; 91596</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52957; 83629</t>
+          <t>52958; 83949</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60299; 102880</t>
+          <t>81320; 106997</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41823</t>
+          <t>46712</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41823</t>
+          <t>46712</t>
         </is>
       </c>
     </row>
@@ -1895,32 +1895,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>22043; 46345</t>
+          <t>22633; 47481</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>23675; 48400</t>
+          <t>22669; 47854</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32994; 51620</t>
+          <t>37326; 58135</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22043; 46345</t>
+          <t>22633; 47481</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>23675; 48400</t>
+          <t>22669; 47854</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32994; 51620</t>
+          <t>37326; 58135</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29483</t>
+          <t>32888</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29483</t>
+          <t>32888</t>
         </is>
       </c>
     </row>
@@ -2013,32 +2013,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11846; 29198</t>
+          <t>11863; 30874</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13231; 31030</t>
+          <t>12556; 31815</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8415; 55759</t>
+          <t>25413; 42294</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11846; 29198</t>
+          <t>11863; 30874</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13231; 31030</t>
+          <t>12556; 31815</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8415; 55759</t>
+          <t>25413; 42294</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20674</t>
+          <t>22405</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20674</t>
+          <t>22405</t>
         </is>
       </c>
     </row>
@@ -2131,32 +2131,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5616; 19143</t>
+          <t>5868; 19472</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2543; 17287</t>
+          <t>2547; 16780</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14926; 28153</t>
+          <t>16436; 29627</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5616; 19143</t>
+          <t>5868; 19472</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2543; 17287</t>
+          <t>2547; 16780</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14926; 28153</t>
+          <t>16436; 29627</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>246124</t>
+          <t>270325</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>246124</t>
+          <t>270325</t>
         </is>
       </c>
     </row>
@@ -2249,32 +2249,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>202807; 265865</t>
+          <t>202798; 263179</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>180886; 238679</t>
+          <t>183949; 238421</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>161854; 293714</t>
+          <t>247339; 297997</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>202807; 265865</t>
+          <t>202798; 263179</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>180886; 238679</t>
+          <t>183949; 238421</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>161854; 293714</t>
+          <t>247339; 297997</t>
         </is>
       </c>
     </row>
